--- a/presentation/SF1-MCU/anomalies.xlsx
+++ b/presentation/SF1-MCU/anomalies.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U88"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1807,36 +1807,36 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13440163</v>
+        <v>13440110</v>
       </c>
       <c r="B16" t="n">
-        <v>4002537897</v>
+        <v>4002537834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>INSPECTION SYSTEMATIQUE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OR004002537897</t>
+          <t>OR004002537834</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-000CP6-P1414B</t>
+          <t>SF01-UT-00PC-ELECTR-00GTA1-TURB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU DE DILUTION B VERS CP6</t>
+          <t>GROUPE TURBINE GTA1 CENTRALE MC</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>S-PC-P1414B</t>
+          <t>S-PC-FC02T</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>LANC CCRP PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1870,17 +1870,17 @@
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q16" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1890,16 +1890,16 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13440290</v>
+        <v>13440163</v>
       </c>
       <c r="B17" t="n">
-        <v>4002538023</v>
+        <v>4002537897</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1908,24 +1908,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OR004002538023</t>
+          <t>OR004002537897</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-0SEMII-PPUI02</t>
+          <t>SF01-UT-0TED-000CP6-P1414B</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MOTOPOMPE D'EPUISEMENT 02 SEM II DE MC</t>
+          <t>MOTOPOMPE EAU DE DILUTION B VERS CP6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>S-PC-SEM-PEPUI1</t>
+          <t>S-PC-P1414B</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1985,36 +1985,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13440336</v>
+        <v>13440181</v>
       </c>
       <c r="B18" t="n">
-        <v>4002538039</v>
+        <v>4002537925</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INSPECTION SYSTEMATIQUE</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OR004002538039</t>
+          <t>OR004002537925</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-ELECTR-00GTA2-LUBR-REFROID1</t>
+          <t>SF01-UT-0TED-000CP6-P1418B</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>REFROIDISSEUR HUILE SUPERIEUR GTA2  MC</t>
+          <t>MOTOPOMPE B INJECTION ACIDE VERS CP6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>S-PC-2MAV30</t>
+          <t>S-PC-P1418B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>LANC CCRP PART RIMP TEC  TàLT</t>
+          <t>LANC CCRP PART RIMP</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2048,17 +2048,17 @@
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2068,42 +2068,42 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13440337</v>
+        <v>13440239</v>
       </c>
       <c r="B19" t="n">
-        <v>4002538140</v>
+        <v>4002538022</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INSPECTION SYSTEMATIQUE</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OR004002538140</t>
+          <t>OR004002538022</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-EAUBRU-FLTRE2</t>
+          <t>SF01-UT-FDEM-0SEMII-PPUI01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FILTRE A SABLE N 02</t>
+          <t>MOTOPOMPE D'EPUISEMENT 01 SEM II DE MC</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>S-PC-FS2</t>
+          <t>S-PC-SEM-PEPUI2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>LANC CCRP PART RIMP TEC  TàLT</t>
+          <t>LANC CCRP PART RIMP</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2137,17 +2137,17 @@
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>46254</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2157,42 +2157,42 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13440398</v>
+        <v>13440290</v>
       </c>
       <c r="B20" t="n">
-        <v>4002538172</v>
+        <v>4002538023</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OR004002538172</t>
+          <t>OR004002538023</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP06B</t>
+          <t>SF01-UT-FDEM-0SEMII-PPUI02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MOTOPOMPE DESSABLEMENT IP06B BASSIN  MC</t>
+          <t>MOTOPOMPE D'EPUISEMENT 02 SEM II DE MC</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>S-PC-924IP05B</t>
+          <t>S-PC-SEM-PEPUI1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>LANC CCRP PART RIMP TEC  TàLT</t>
+          <t>LANC CCRP PART RIMP</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2232,11 +2232,11 @@
         <v>46254</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2246,42 +2246,42 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13563581</v>
+        <v>13440336</v>
       </c>
       <c r="B21" t="n">
-        <v>4002654274</v>
+        <v>4002538039</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>INSPECTION SYSTEMATIQUE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OR004002654274</t>
+          <t>OR004002538039</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-FLTRT2</t>
+          <t>SF01-UT-00PC-ELECTR-00GTA2-LUBR-REFROID1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FILTRE ROTATIVE N02 BASSIN EAU DE MER MC</t>
+          <t>REFROIDISSEUR HUILE SUPERIEUR GTA2  MC</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>S-PC-BEAUDREY-2</t>
+          <t>S-PC-2MAV30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>LANC CCRP PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2311,21 +2311,21 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>IP1020260904</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
         <v>46291</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>46269</v>
+        <v>46254</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2335,42 +2335,42 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13667577</v>
+        <v>13440337</v>
       </c>
       <c r="B22" t="n">
-        <v>4002751698</v>
+        <v>4002538140</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>INSPECTION SYSTEMATIQUE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OR004002751698</t>
+          <t>OR004002538140</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-000CP5-P1201A</t>
+          <t>SF01-UT-0TED-EAUBRU-FLTRE2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A ALIMENTATION CP5 EAU FILTREE</t>
+          <t>FILTRE A SABLE N 02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>S-PC-P12-01A</t>
+          <t>S-PC-FS2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2400,21 +2400,21 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
         <v>46291</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>46278</v>
+        <v>46254</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2424,42 +2424,42 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>13667581</v>
+        <v>13440380</v>
       </c>
       <c r="B23" t="n">
-        <v>4002751705</v>
+        <v>4002538143</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>INSPECTION SYSTEMATIQUE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OR004002751705</t>
+          <t>OR004002538143</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-ELECTR-PCODA1</t>
+          <t>SF01-UT-0TED-EAUBRU-FLTRE4</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>POMPE ÉXTRACTION CONDENSAT A GTA1 MC</t>
+          <t>FILTRE A SABLE N 04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>S-PC-P1LCB10AP110</t>
+          <t>S-PC-FS4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2489,21 +2489,21 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>46278</v>
+        <v>46254</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2513,42 +2513,42 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>13667582</v>
+        <v>13440398</v>
       </c>
       <c r="B24" t="n">
-        <v>4002751706</v>
+        <v>4002538172</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OR004002751706</t>
+          <t>OR004002538172</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-ELECTR-PCODA2</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP06B</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>POMPE ÉXTRACTION CONDENSAT A GTA2 MC</t>
+          <t>MOTOPOMPE DESSABLEMENT IP06B BASSIN  MC</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>S-PC-P2LCB10AP110</t>
+          <t>S-PC-924IP05B</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2578,21 +2578,21 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
         <v>46291</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>46278</v>
+        <v>46254</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2602,42 +2602,42 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>13667770</v>
+        <v>13563191</v>
       </c>
       <c r="B25" t="n">
-        <v>4002751714</v>
+        <v>4002653933</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OR004002751714</t>
+          <t>OR004002653933</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-EAUVAP-0FP04B</t>
+          <t>SF01-UT-0TED-000CP5-0D1213</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>POMPE D'EAU CONDENSEE FP04B CENTRALE MC</t>
+          <t>DEGAZEUR CP5 TED PC PSU</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>S-PC-P920 FP 04B</t>
+          <t>S-PC-D12-13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>LANC CCRP PART RIMP TEC  TàLT</t>
+          <t>LANC CCRP PART RIMP</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2667,21 +2667,21 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260904</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>46278</v>
+        <v>46269</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2691,16 +2691,16 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>13667610</v>
+        <v>13563581</v>
       </c>
       <c r="B26" t="n">
-        <v>4002751751</v>
+        <v>4002654274</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2709,24 +2709,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OR004002751751</t>
+          <t>OR004002654274</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-000CP5-P1215A</t>
+          <t>SF01-UT-FDEM-BASSIN-FLTRT2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A DE DILUTION VERS MB5</t>
+          <t>FILTRE ROTATIVE N02 BASSIN EAU DE MER MC</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>S-PC-P12-15A</t>
+          <t>S-PC-BEAUDREY-2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>LANC CCRP PART RIMP TEC  TàLT</t>
+          <t>LANC CCRP PART RIMP</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2756,14 +2756,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260904</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
         <v>46291</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>46278</v>
+        <v>46269</v>
       </c>
       <c r="R26" t="n">
         <v>2</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13667613</v>
+        <v>13667577</v>
       </c>
       <c r="B27" t="n">
-        <v>4002751754</v>
+        <v>4002751698</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2798,24 +2798,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OR004002751754</t>
+          <t>OR004002751698</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-000CP5-P1215B</t>
+          <t>SF01-UT-0TED-000CP5-P1201A</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MOTOPOMPE B DE DILUTION VERS MB5</t>
+          <t>MOTOPOMPE A ALIMENTATION CP5 EAU FILTREE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>S-PC-P12-15B</t>
+          <t>S-PC-P12-01A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2875,10 +2875,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13667642</v>
+        <v>13667581</v>
       </c>
       <c r="B28" t="n">
-        <v>4002751773</v>
+        <v>4002751705</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2887,24 +2887,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OR004002751773</t>
+          <t>OR004002751705</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-000CP6-P1415A</t>
+          <t>SF01-UT-00PC-ELECTR-PCODA1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU DE DILUTION A VERS MB6</t>
+          <t>POMPE ÉXTRACTION CONDENSAT A GTA1 MC</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>S-PC-P1415A</t>
+          <t>S-PC-P1LCB10AP110</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2964,10 +2964,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>13667688</v>
+        <v>13667582</v>
       </c>
       <c r="B29" t="n">
-        <v>4002751830</v>
+        <v>4002751706</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2976,24 +2976,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OR004002751830</t>
+          <t>OR004002751706</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-EAUVAP-0FP02A</t>
+          <t>SF01-UT-00PC-ELECTR-PCODA2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MOTOPOMPE PRE-ALIMENTAIRE FP02A  PC-MC</t>
+          <t>POMPE ÉXTRACTION CONDENSAT A GTA2 MC</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>S-PC-P920 FP 02A</t>
+          <t>S-PC-P2LCB10AP110</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>13667728</v>
+        <v>13667583</v>
       </c>
       <c r="B30" t="n">
-        <v>4002751869</v>
+        <v>4002751707</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3065,24 +3065,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OR004002751869</t>
+          <t>OR004002751707</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-STOCKE-0P1212</t>
+          <t>SF01-UT-00PC-ELECTR-PCODB1-ASSI-00POMPE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MOTOPOMPE RE-CIRCULATION VERS CP5</t>
+          <t>POMPE ÉXTRACTION CONDENSAT B GTA1 MC</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>S-PC-P12-12</t>
+          <t>S-PC-P1LCB20AP110</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q30" s="2" t="n">
         <v>46278</v>
@@ -3142,36 +3142,36 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13667719</v>
+        <v>13667589</v>
       </c>
       <c r="B31" t="n">
-        <v>4002751884</v>
+        <v>4002751713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RONDE INPECTION ZONE C</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OR004002751884</t>
+          <t>OR004002751713</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SF01-UT</t>
+          <t>SF01-UT-00PC-EAUVAP-0FP04B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTILITE ENERGIE ET FLUIDE MAROC CHIMIE</t>
+          <t>POMPE D'EAU CONDENSEE FP04B CENTRALE MC</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SA-PC-PC</t>
+          <t>S-PC-P920 FP 04B</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3205,17 +3205,17 @@
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q31" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3225,42 +3225,42 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13667753</v>
+        <v>13667770</v>
       </c>
       <c r="B32" t="n">
-        <v>4002751888</v>
+        <v>4002751714</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OR004002751888</t>
+          <t>OR004002751714</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP01A</t>
+          <t>SF01-UT-00PC-EAUVAP-0FP04B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS CENTRALE IPO1A MC</t>
+          <t>POMPE D'EAU CONDENSEE FP04B CENTRALE MC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>S-PC-P924 IP 01A</t>
+          <t>S-PC-P920 FP 04B</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3300,11 +3300,11 @@
         <v>46278</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3314,42 +3314,42 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>13667756</v>
+        <v>13667605</v>
       </c>
       <c r="B33" t="n">
-        <v>4002751891</v>
+        <v>4002751746</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OR004002751891</t>
+          <t>OR004002751746</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP01B</t>
+          <t>SF01-UT-0TED-000CP5-P1214A</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS CENTRALE IPO1B MC</t>
+          <t>MOTOPOMPE A DE DILUTION VERS CP5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>S-PC-P924 IP 01B</t>
+          <t>S-PC-P12-14A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3383,17 +3383,17 @@
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3403,42 +3403,42 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>13667758</v>
+        <v>13667610</v>
       </c>
       <c r="B34" t="n">
-        <v>4002751893</v>
+        <v>4002751751</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OR004002751893</t>
+          <t>OR004002751751</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP02A</t>
+          <t>SF01-UT-0TED-000CP5-P1215A</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS SEM2 IPO2A MC</t>
+          <t>MOTOPOMPE A DE DILUTION VERS MB5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>S-PC-P924 IP 02A</t>
+          <t>S-PC-P12-15A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3478,11 +3478,11 @@
         <v>46278</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3492,16 +3492,16 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13667739</v>
+        <v>13667613</v>
       </c>
       <c r="B35" t="n">
-        <v>4002751900</v>
+        <v>4002751754</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3510,24 +3510,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OR004002751900</t>
+          <t>OR004002751754</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-STOCKE-P1204A</t>
+          <t>SF01-UT-0TED-000CP5-P1215B</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A E/DEC BAC 1000 VES PSIII</t>
+          <t>MOTOPOMPE B DE DILUTION VERS MB5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>S-PC-P12-04A</t>
+          <t>S-PC-P12-15B</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3587,10 +3587,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13667743</v>
+        <v>13667622</v>
       </c>
       <c r="B36" t="n">
-        <v>4002751904</v>
+        <v>4002751763</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3599,24 +3599,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OR004002751904</t>
+          <t>OR004002751763</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-EAUFLT-PPEF02</t>
+          <t>SF01-UT-0TED-000CP6-P1401A</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU FILTREE VERS CHATEAU N 02</t>
+          <t>MOTOPOMPE DE GAVAGE A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>S-PC-KA066</t>
+          <t>S-PC-P1401A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>46278</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13667763</v>
+        <v>13667642</v>
       </c>
       <c r="B37" t="n">
-        <v>4002751914</v>
+        <v>4002751773</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -3688,24 +3688,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OR004002751914</t>
+          <t>OR004002751773</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-EAUVAP-0FP04A</t>
+          <t>SF01-UT-0TED-000CP6-P1415A</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>POMPE D'EAU CONDENSEE FP04A CENTRALE MC</t>
+          <t>MOTOPOMPE EAU DE DILUTION A VERS MB6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>S-PC-P920 FP 04A</t>
+          <t>S-PC-P1415A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3765,10 +3765,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13667769</v>
+        <v>13667688</v>
       </c>
       <c r="B38" t="n">
-        <v>4002751920</v>
+        <v>4002751830</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -3777,24 +3777,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OR004002751920</t>
+          <t>OR004002751830</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-EAUVAP-0FP03B</t>
+          <t>SF01-UT-00PC-EAUVAP-0FP02A</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU ALIMENTAIRE FP03B PC-MC</t>
+          <t>MOTOPOMPE PRE-ALIMENTAIRE FP02A  PC-MC</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>S-PC-P920 FP 03B</t>
+          <t>S-PC-P920 FP 02A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3854,36 +3854,36 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10143561</v>
+        <v>13667728</v>
       </c>
       <c r="B39" t="n">
-        <v>4189446</v>
+        <v>4002751869</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Démontage coude Noria A pour débouchage</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OR000004189446</t>
+          <t>OR004002751869</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
+          <t>SF01-UT-0TED-STOCKE-0P1212</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
+          <t>MOTOPOMPE RE-CIRCULATION VERS CP5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>S-PC-922 IE 01A</t>
+          <t>S-PC-P12-12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3913,66 +3913,66 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>45712</v>
+        <v>46278</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10143568</v>
+        <v>13667731</v>
       </c>
       <c r="B40" t="n">
-        <v>4189458</v>
+        <v>4002751872</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Démontage coude Noria B pour débouchage</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OR000004189458</t>
+          <t>OR004002751872</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-0NORIA-0IE01B</t>
+          <t>SF01-UT-00PC-0NORIA-PPNORA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ECHANGEUR NORIA-B CENTRALE MC</t>
+          <t>MOTOPOMPE NORIA-A CENTRALE MC</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>S-PC-922 IE 01B</t>
+          <t>S-PC-P922 IP 01A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4002,64 +4002,66 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>45712</v>
+        <v>46278</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="n">
+        <v>13667736</v>
+      </c>
       <c r="B41" t="n">
-        <v>4189572</v>
+        <v>4002751876</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Contrôle pompe de Transfer N°2</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OR000004189572</t>
+          <t>OR004002751876</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-STFUEL-PPETF2</t>
+          <t>SF01-UT-0TED-STOCKE-P1203B</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>POMPE DE TRANSFERT DE FUEL N 02</t>
+          <t>MOTOPOMP B E/DEC BAC1000 VERS BACHE ALIM</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>S-PC-PTF2</t>
+          <t>S-PC-P12-03B</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4079,7 +4081,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4089,64 +4091,66 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>45712</v>
+        <v>46278</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="n">
+        <v>13667719</v>
+      </c>
       <c r="B42" t="n">
-        <v>4198614</v>
+        <v>4002751884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remise en état passerelle</t>
+          <t>RONDE INPECTION ZONE C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OR000004198614</t>
+          <t>OR004002751884</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-BAC100</t>
+          <t>SF01-UT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BAC FUEL 100 M3 CHAUDIERE BW MC</t>
+          <t>UTILITE ENERGIE ET FLUIDE MAROC CHIMIE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>S-PC-BW-CITERNE FUEL</t>
+          <t>SA-PC-PC</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4166,7 +4170,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4176,64 +4180,66 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>45713</v>
+        <v>46278</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="n">
+        <v>13667750</v>
+      </c>
       <c r="B43" t="n">
-        <v>4198724</v>
+        <v>4002751885</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Changement pompe de fuel N°1</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OR000004198724</t>
+          <t>OR004002751885</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-PPHPF1</t>
+          <t>SF01-UT-0TED-EAUFLT-0KA068</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>POMPE HP FUEL N 01 CHAUDIERE BW MC</t>
+          <t>MOTOPOMPE EAU SANITAIRE N 01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>S-PC-BW-PG2</t>
+          <t>S-PC-KA068</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4253,7 +4259,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4263,62 +4269,68 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>45713</v>
+        <v>46278</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="n">
+        <v>13667753</v>
+      </c>
       <c r="B44" t="n">
-        <v>4198842</v>
+        <v>4002751888</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Démontage de la pompe IP05A</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OR000004198842</t>
+          <t>OR004002751888</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP01A</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ZONE BASSIN EAU DE MER MC</t>
+          <t>MOTOPOMPE EAU MER VERS CENTRALE IPO1A MC</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>S-PC-P924 IP 01A</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -4336,7 +4348,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4346,66 +4358,66 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>45713</v>
+        <v>46278</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10164180</v>
+        <v>13667755</v>
       </c>
       <c r="B45" t="n">
-        <v>4198845</v>
+        <v>4002751890</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ouverture et fermeture des  PV du BW2</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OR000004198845</t>
+          <t>OR004002751890</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP01B</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+          <t>MOTOPOMPE EAU MER VERS CENTRALE IPO1B MC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>S-PC-B2</t>
+          <t>S-PC-P924 IP 01B</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4425,7 +4437,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4435,66 +4447,66 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P45" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>45713</v>
+        <v>46278</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10159310</v>
+        <v>13667756</v>
       </c>
       <c r="B46" t="n">
-        <v>4198846</v>
+        <v>4002751891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Montage des affiches de signalisation</t>
+          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OR000004198846</t>
+          <t>OR004002751891</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-PPHPF1</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP01B</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>POMPE HP FUEL N 01 CHAUDIERE BW MC</t>
+          <t>MOTOPOMPE EAU MER VERS CENTRALE IPO1B MC</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>S-PC-BW-PG2</t>
+          <t>S-PC-P924 IP 01B</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4514,7 +4526,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4524,64 +4536,66 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>45713</v>
+        <v>46278</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="n">
+        <v>13667757</v>
+      </c>
       <c r="B47" t="n">
-        <v>4200816</v>
+        <v>4002751892</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remise en état du circuit d'aire</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>OR000004200816</t>
+          <t>OR004002751892</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-000CP5-0K1212</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP02A</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SUPRESSEUR D AIR B CP5</t>
+          <t>MOTOPOMPE EAU MER VERS SEM2 IPO2A MC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>S-PC-K12-12</t>
+          <t>S-PC-P924 IP 02A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4601,7 +4615,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4611,64 +4625,66 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="n">
+        <v>13667758</v>
+      </c>
       <c r="B48" t="n">
-        <v>4201746</v>
+        <v>4002751893</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Changement tresse de la pompe IP05B</t>
+          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>OR000004201746</t>
+          <t>OR004002751893</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP05B</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP02A</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MOTOPOMPE IP05B EAU MER VERS PS4</t>
+          <t>MOTOPOMPE EAU MER VERS SEM2 IPO2A MC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>S-PC-924-IP-05B</t>
+          <t>S-PC-P924 IP 02A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4688,7 +4704,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4698,64 +4714,66 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="n">
+        <v>13667800</v>
+      </c>
       <c r="B49" t="n">
-        <v>4202360</v>
+        <v>4002751895</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Découpage et montage des tôle</t>
+          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OR000004202360</t>
+          <t>OR004002751895</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-0SEMII</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP02B</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ZONE SURPRESSEUR EAU DE MER II DE MC</t>
+          <t>MOTOPOMPE EAU MER VERS SEM2 IPO2B</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SA-PC-PC-SEM</t>
+          <t>S-PC-P924 IP 02B</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4775,7 +4793,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4785,64 +4803,66 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="n">
+        <v>13667739</v>
+      </c>
       <c r="B50" t="n">
-        <v>4202376</v>
+        <v>4002751900</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Démontage pompe Transfer fuel N°1 et leu</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OR000004202376</t>
+          <t>OR004002751900</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-PPHPF1</t>
+          <t>SF01-UT-0TED-STOCKE-P1204A</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>POMPE HP FUEL N 01 CHAUDIERE BW MC</t>
+          <t>MOTOPOMPE A E/DEC BAC 1000 VES PSIII</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>S-PC-BW-PG2</t>
+          <t>S-PC-P12-04A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4862,7 +4882,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4872,66 +4892,66 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10143453</v>
+        <v>13667743</v>
       </c>
       <c r="B51" t="n">
-        <v>4202623</v>
+        <v>4002751904</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Démontage et remontage pompe Transfer fu</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OR000004202623</t>
+          <t>OR004002751904</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-PPHPF1</t>
+          <t>SF01-UT-0TED-EAUFLT-PPEF02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>POMPE HP FUEL N 01 CHAUDIERE BW MC</t>
+          <t>MOTOPOMPE EAU FILTREE VERS CHATEAU N 02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>S-PC-BW-PG2</t>
+          <t>S-PC-KA066</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4951,7 +4971,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4961,64 +4981,66 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="n">
+        <v>13667744</v>
+      </c>
       <c r="B52" t="n">
-        <v>4202720</v>
+        <v>4002751905</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Préparation et soudage bride d'aspiratio</t>
+          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OR000004202720</t>
+          <t>OR004002751905</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP04A</t>
+          <t>SF01-UT-0TED-EAUFLT-PP1MC1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS PPII IPO4A BASSIN</t>
+          <t>MOTOPOMPE EAU FILTREE VERS MC1 N01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>S-PC-P924 IP 04A</t>
+          <t>S-PC-P8</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5038,7 +5060,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5048,64 +5070,66 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P52" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="n">
+        <v>13667748</v>
+      </c>
       <c r="B53" t="n">
-        <v>4202735</v>
+        <v>4002751909</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Découpage et remontage garde-corps déven</t>
+          <t>OMS_MESURE VIBRATOIRE PALIERS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OR000004202735</t>
+          <t>OR004002751909</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-STFUEL</t>
+          <t>SF01-UT-0TED-EAUFLT-PP1MC2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>STATION DE FUEL UTILITE DE MC</t>
+          <t>MOTOPOMPE EAU FILTREE VERS MC2 N01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SA-PC-PC-SFUEL</t>
+          <t>S-PC-PEF1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5125,7 +5149,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5135,64 +5159,66 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P53" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="n">
+        <v>13667763</v>
+      </c>
       <c r="B54" t="n">
-        <v>4202736</v>
+        <v>4002751914</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Démontage coude Noria A  pour débouchage</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OR000004202736</t>
+          <t>OR004002751914</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
+          <t>SF01-UT-00PC-EAUVAP-0FP04A</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
+          <t>POMPE D'EAU CONDENSEE FP04A CENTRALE MC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>S-PC-922 IE 01A</t>
+          <t>S-PC-P920 FP 04A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5212,7 +5238,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5222,62 +5248,68 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P54" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="n">
+        <v>13667769</v>
+      </c>
       <c r="B55" t="n">
-        <v>4202738</v>
+        <v>4002751920</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Démontage et remontage flexible du pompe</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OR000004202738</t>
+          <t>OR004002751920</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN</t>
+          <t>SF01-UT-00PC-EAUVAP-0FP03B</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ZONE BASSIN EAU DE MER MC</t>
+          <t>MOTOPOMPE EAU ALIMENTAIRE FP03B PC-MC</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>S-PC-P920 FP 03B</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -5295,7 +5327,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5305,47 +5337,49 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q55" s="2" t="n">
-        <v>45714</v>
+        <v>46278</v>
       </c>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="n">
+        <v>10143561</v>
+      </c>
       <c r="B56" t="n">
-        <v>4206252</v>
+        <v>4189446</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Démontage coude Noria A  pour débouchage</t>
+          <t>Démontage coude Noria A pour débouchage</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OR000004206252</t>
+          <t>OR000004189446</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5396,10 +5430,10 @@
         </is>
       </c>
       <c r="P56" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>45716</v>
+        <v>45712</v>
       </c>
       <c r="R56" t="n">
         <v>1</v>
@@ -5421,18 +5455,20 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="n">
+        <v>10143568</v>
+      </c>
       <c r="B57" t="n">
-        <v>4206331</v>
+        <v>4189458</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Démontage coude Noria  B pour débouchage</t>
+          <t>Démontage coude Noria B pour débouchage</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OR000004206331</t>
+          <t>OR000004189458</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5483,10 +5519,10 @@
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>45716</v>
+        <v>45712</v>
       </c>
       <c r="R57" t="n">
         <v>1</v>
@@ -5510,31 +5546,35 @@
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>4207007</v>
+        <v>4189572</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Démontage d'une boulons de le fouloire</t>
+          <t>Contrôle pompe de Transfer N°2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OR000004207007</t>
+          <t>OR000004189572</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP05A-GPPE-PALIER01</t>
+          <t>SF01-UT-00PC-STFUEL-PPETF2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PALIER POMPE IP05A VERS PS4</t>
+          <t>POMPE DE TRANSFERT DE FUEL N 02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>S-PC-PTF2</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -5566,10 +5606,10 @@
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>45716</v>
+        <v>45712</v>
       </c>
       <c r="R58" t="n">
         <v>1</v>
@@ -5593,33 +5633,33 @@
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>4207033</v>
+        <v>4198614</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Préparation supporte de la pompe E/M</t>
+          <t>Remise en état passerelle</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OR000004207033</t>
+          <t>OR000004198614</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP02A</t>
+          <t>SF01-UT-00PC-000BW2-BAC100</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS SEM2 IPO2A MC</t>
+          <t>BAC FUEL 100 M3 CHAUDIERE BW MC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>S-PC-P924 IP 02A</t>
+          <t>S-PC-BW-CITERNE FUEL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5653,10 +5693,10 @@
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>45716</v>
+        <v>45713</v>
       </c>
       <c r="R59" t="n">
         <v>1</v>
@@ -5680,31 +5720,35 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>4207085</v>
+        <v>4198724</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Elimination des tresse sur la pompe IP05</t>
+          <t>Changement pompe de fuel N°1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OR000004207085</t>
+          <t>OR000004198724</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP05A-GPPE-PRSETOUP</t>
+          <t>SF01-UT-00PC-000BW2-PPHPF1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PRESSE ETOUPE POMPE IP05A VERS PS4</t>
+          <t>POMPE HP FUEL N 01 CHAUDIERE BW MC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>S-PC-BW-PG2</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -5736,10 +5780,10 @@
         </is>
       </c>
       <c r="P60" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>45716</v>
+        <v>45713</v>
       </c>
       <c r="R60" t="n">
         <v>1</v>
@@ -5763,35 +5807,31 @@
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>4208410</v>
+        <v>4198842</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ouverture et fermeture de la vanne</t>
+          <t>Démontage de la pompe IP05A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OR000004208410</t>
+          <t>OR000004198842</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP03A</t>
+          <t>SF01-UT-FDEM-BASSIN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS PSII IPO3A BASSIN</t>
+          <t>ZONE BASSIN EAU DE MER MC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>S-PC-P924 IP 03A</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -5823,10 +5863,10 @@
         </is>
       </c>
       <c r="P61" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>45717</v>
+        <v>45713</v>
       </c>
       <c r="R61" t="n">
         <v>1</v>
@@ -5848,35 +5888,37 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="n">
+        <v>10164180</v>
+      </c>
       <c r="B62" t="n">
-        <v>4208411</v>
+        <v>4198845</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Changement tresse de la pompe IP03A</t>
+          <t>ouverture et fermeture des  PV du BW2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OR000004208411</t>
+          <t>OR000004198845</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP03A</t>
+          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS PSII IPO3A BASSIN</t>
+          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>S-PC-P924 IP 03A</t>
+          <t>S-PC-B2</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5910,10 +5952,10 @@
         </is>
       </c>
       <c r="P62" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>45717</v>
+        <v>45713</v>
       </c>
       <c r="R62" t="n">
         <v>1</v>
@@ -5935,35 +5977,37 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="n">
+        <v>10159310</v>
+      </c>
       <c r="B63" t="n">
-        <v>4208412</v>
+        <v>4198846</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Démontage coude Noria A  pour débouchage</t>
+          <t>Montage des affiches de signalisation</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OR000004208412</t>
+          <t>OR000004198846</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
+          <t>SF01-UT-00PC-000BW2-PPHPF1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
+          <t>POMPE HP FUEL N 01 CHAUDIERE BW MC</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>S-PC-922 IE 01A</t>
+          <t>S-PC-BW-PG2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5997,10 +6041,10 @@
         </is>
       </c>
       <c r="P63" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q63" s="2" t="n">
-        <v>45717</v>
+        <v>45713</v>
       </c>
       <c r="R63" t="n">
         <v>1</v>
@@ -6024,33 +6068,33 @@
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>4208414</v>
+        <v>4200816</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Démontage coude Noria  B pour débouchage</t>
+          <t>Remise en état du circuit d'aire</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OR000004208414</t>
+          <t>OR000004200816</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-0NORIA-0IE01B</t>
+          <t>SF01-UT-0TED-000CP5-0K1212</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ECHANGEUR NORIA-B CENTRALE MC</t>
+          <t>SUPRESSEUR D AIR B CP5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>S-PC-922 IE 01B</t>
+          <t>S-PC-K12-12</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6084,10 +6128,10 @@
         </is>
       </c>
       <c r="P64" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="R64" t="n">
         <v>1</v>
@@ -6111,33 +6155,33 @@
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>4208417</v>
+        <v>4201746</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serrage des tresse de la pompe IP03A</t>
+          <t>Changement tresse de la pompe IP05B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OR000004208417</t>
+          <t>OR000004201746</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP03A</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP05B</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS PSII IPO3A BASSIN</t>
+          <t>MOTOPOMPE IP05B EAU MER VERS PS4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>S-PC-P924 IP 03A</t>
+          <t>S-PC-924-IP-05B</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6171,10 +6215,10 @@
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="R65" t="n">
         <v>1</v>
@@ -6198,33 +6242,33 @@
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>4208418</v>
+        <v>4202360</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Etanchement fuite vapeur au niveau bride</t>
+          <t>Découpage et montage des tôle</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OR000004208418</t>
+          <t>OR000004202360</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-EAUVAP-20FR04</t>
+          <t>SF01-UT-FDEM-0SEMII</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>COLLECTEUR BARILLET VAPEUR MP</t>
+          <t>ZONE SURPRESSEUR EAU DE MER II DE MC</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>S-PC-920FR04</t>
+          <t>SA-PC-PC-SEM</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6258,10 +6302,10 @@
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="R66" t="n">
         <v>1</v>
@@ -6283,37 +6327,35 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>10164242</v>
-      </c>
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>4210032</v>
+        <v>4202376</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Démontage et remontage deux bruleur</t>
+          <t>Démontage pompe Transfer fuel N°1 et leu</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OR000004210032</t>
+          <t>OR000004202376</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+          <t>SF01-UT-00PC-000BW2-PPHPF1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+          <t>POMPE HP FUEL N 01 CHAUDIERE BW MC</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>S-PC-B2</t>
+          <t>S-PC-BW-PG2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6347,10 +6389,10 @@
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>45719</v>
+        <v>45714</v>
       </c>
       <c r="R67" t="n">
         <v>1</v>
@@ -6372,35 +6414,37 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="n">
+        <v>10143453</v>
+      </c>
       <c r="B68" t="n">
-        <v>4210037</v>
+        <v>4202623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Travaux sur diaphragme sortie vapeur BW2</t>
+          <t>Démontage et remontage pompe Transfer fu</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OR000004210037</t>
+          <t>OR000004202623</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+          <t>SF01-UT-00PC-000BW2-PPHPF1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+          <t>POMPE HP FUEL N 01 CHAUDIERE BW MC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>S-PC-B2</t>
+          <t>S-PC-BW-PG2</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6434,10 +6478,10 @@
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>45719</v>
+        <v>45714</v>
       </c>
       <c r="R68" t="n">
         <v>1</v>
@@ -6459,37 +6503,35 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>10170802</v>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>4210182</v>
+        <v>4202720</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Démontage et remontage pompe Transfer</t>
+          <t>Préparation et soudage bride d'aspiratio</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>OR000004210182</t>
+          <t>OR000004202720</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-STFUEL-PPETF1</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP04A</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>POMPE DE TRANSFERT DE FUEL N 01</t>
+          <t>MOTOPOMPE EAU MER VERS PPII IPO4A BASSIN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>S-PC-PTF1</t>
+          <t>S-PC-P924 IP 04A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6523,10 +6565,10 @@
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>45719</v>
+        <v>45714</v>
       </c>
       <c r="R69" t="n">
         <v>1</v>
@@ -6550,33 +6592,33 @@
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>4210188</v>
+        <v>4202735</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Démontage et remontage filtre HP au BW</t>
+          <t>Découpage et remontage garde-corps déven</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OR000004210188</t>
+          <t>OR000004202735</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-EAUVAP-HPVAPE</t>
+          <t>SF01-UT-00PC-STFUEL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CIRCUIT VAPEUR HP DE LA CENTRALE  PC</t>
+          <t>STATION DE FUEL UTILITE DE MC</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>S-PC-PC-VAPHP</t>
+          <t>SA-PC-PC-SFUEL</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6610,10 +6652,10 @@
         </is>
       </c>
       <c r="P70" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>45719</v>
+        <v>45714</v>
       </c>
       <c r="R70" t="n">
         <v>1</v>
@@ -6637,33 +6679,33 @@
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>4210191</v>
+        <v>4202736</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Etanchement fuite de vapeur de diaphragm</t>
+          <t>Démontage coude Noria A  pour débouchage</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OR000004210191</t>
+          <t>OR000004202736</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>S-PC-B2</t>
+          <t>S-PC-922 IE 01A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6697,10 +6739,10 @@
         </is>
       </c>
       <c r="P71" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q71" s="2" t="n">
-        <v>45719</v>
+        <v>45714</v>
       </c>
       <c r="R71" t="n">
         <v>1</v>
@@ -6722,39 +6764,33 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>10127258</v>
-      </c>
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>4210350</v>
+        <v>4202738</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Démontage coude Noria A  pour débouchage</t>
+          <t>Démontage et remontage flexible du pompe</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OR000004210350</t>
+          <t>OR000004202738</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
+          <t>SF01-UT-FDEM-BASSIN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
+          <t>ZONE BASSIN EAU DE MER MC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>S-PC-922 IE 01A</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -6786,10 +6822,10 @@
         </is>
       </c>
       <c r="P72" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q72" s="2" t="n">
-        <v>45719</v>
+        <v>45714</v>
       </c>
       <c r="R72" t="n">
         <v>1</v>
@@ -6811,37 +6847,35 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>10127275</v>
-      </c>
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>4210352</v>
+        <v>4206252</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Démontage coude Noria  B pour débouchage</t>
+          <t>Démontage coude Noria A  pour débouchage</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OR000004210352</t>
+          <t>OR000004206252</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-0NORIA-0IE01B</t>
+          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ECHANGEUR NORIA-B CENTRALE MC</t>
+          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>S-PC-922 IE 01B</t>
+          <t>S-PC-922 IE 01A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6878,7 +6912,7 @@
         <v>46290</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>45719</v>
+        <v>45716</v>
       </c>
       <c r="R73" t="n">
         <v>1</v>
@@ -6902,33 +6936,33 @@
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>4211596</v>
+        <v>4206331</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Etanchement fuit vapeur sur bruleur BW2</t>
+          <t>Démontage coude Noria  B pour débouchage</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OR000004211596</t>
+          <t>OR000004206331</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+          <t>SF01-UT-00PC-0NORIA-0IE01B</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+          <t>ECHANGEUR NORIA-B CENTRALE MC</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>S-PC-B2</t>
+          <t>S-PC-922 IE 01B</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6965,7 +6999,7 @@
         <v>46290</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>45720</v>
+        <v>45716</v>
       </c>
       <c r="R74" t="n">
         <v>1</v>
@@ -6989,35 +7023,31 @@
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>4212499</v>
+        <v>4207007</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Décoincement de la vanne de vapeur BW2</t>
+          <t>Démontage d'une boulons de le fouloire</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OR000004212499</t>
+          <t>OR000004207007</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP05A-GPPE-PALIER01</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+          <t>PALIER POMPE IP05A VERS PS4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>S-PC-B2</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -7052,7 +7082,7 @@
         <v>46290</v>
       </c>
       <c r="Q75" s="2" t="n">
-        <v>45720</v>
+        <v>45716</v>
       </c>
       <c r="R75" t="n">
         <v>1</v>
@@ -7076,33 +7106,33 @@
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>4212565</v>
+        <v>4207033</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Démontage et remontage manchette</t>
+          <t>Préparation supporte de la pompe E/M</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OR000004212565</t>
+          <t>OR000004207033</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-000CP5-P1211A</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP02A</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MOTOPOMPE DE REPRISE A</t>
+          <t>MOTOPOMPE EAU MER VERS SEM2 IPO2A MC</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>S-PC-P12-11A</t>
+          <t>S-PC-P924 IP 02A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7139,7 +7169,7 @@
         <v>46290</v>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>45720</v>
+        <v>45716</v>
       </c>
       <c r="R76" t="n">
         <v>1</v>
@@ -7161,39 +7191,33 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>10127378</v>
-      </c>
+      <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>4212573</v>
+        <v>4207085</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pose chassis de la pompe BP vers PP1</t>
+          <t>Elimination des tresse sur la pompe IP05</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OR000004212573</t>
+          <t>OR000004207085</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-0SEMII-P1303B</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP05A-GPPE-PRSETOUP</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER PPI P1303B SEM II MC</t>
+          <t>PRESSE ETOUPE POMPE IP05A VERS PS4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>S-PC-P1303B</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -7228,7 +7252,7 @@
         <v>46290</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>45720</v>
+        <v>45716</v>
       </c>
       <c r="R77" t="n">
         <v>1</v>
@@ -7252,33 +7276,33 @@
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>4219072</v>
+        <v>4208410</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Démontage coude Noria A  pour débouchage</t>
+          <t>Ouverture et fermeture de la vanne</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OR000004219072</t>
+          <t>OR000004208410</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP03A</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
+          <t>MOTOPOMPE EAU MER VERS PSII IPO3A BASSIN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>S-PC-922 IE 01A</t>
+          <t>S-PC-P924 IP 03A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7315,7 +7339,7 @@
         <v>46290</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>45721</v>
+        <v>45717</v>
       </c>
       <c r="R78" t="n">
         <v>1</v>
@@ -7339,33 +7363,33 @@
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>4219078</v>
+        <v>4208411</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Etanchement deux fuite de vapeur circuit</t>
+          <t>Changement tresse de la pompe IP03A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OR000004219078</t>
+          <t>OR000004208411</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP03A</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+          <t>MOTOPOMPE EAU MER VERS PSII IPO3A BASSIN</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>S-PC-B2</t>
+          <t>S-PC-P924 IP 03A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7402,7 +7426,7 @@
         <v>46290</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>45721</v>
+        <v>45717</v>
       </c>
       <c r="R79" t="n">
         <v>1</v>
@@ -7426,33 +7450,33 @@
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>4219849</v>
+        <v>4208412</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>débridage de l'aspiration de la pompe Su</t>
+          <t>Démontage coude Noria A  pour débouchage</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>OR000004219849</t>
+          <t>OR000004208412</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-0SEMII-P1303A</t>
+          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER PPI P1303A SEM II MC</t>
+          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>S-PC-P1303A</t>
+          <t>S-PC-922 IE 01A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7489,7 +7513,7 @@
         <v>46290</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>45721</v>
+        <v>45717</v>
       </c>
       <c r="R80" t="n">
         <v>1</v>
@@ -7513,33 +7537,33 @@
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>4228040</v>
+        <v>4208414</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serrage des tresse pompe IP02B</t>
+          <t>Démontage coude Noria  B pour débouchage</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OR000004228040</t>
+          <t>OR000004208414</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SF01-UT-FDEM-BASSIN-0IP02B</t>
+          <t>SF01-UT-00PC-0NORIA-0IE01B</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MOTOPOMPE EAU MER VERS SEM2 IPO2B</t>
+          <t>ECHANGEUR NORIA-B CENTRALE MC</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>S-PC-P924 IP 02B</t>
+          <t>S-PC-922 IE 01B</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7576,7 +7600,7 @@
         <v>46290</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>45722</v>
+        <v>45717</v>
       </c>
       <c r="R81" t="n">
         <v>1</v>
@@ -7600,33 +7624,33 @@
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>4240411</v>
+        <v>4208417</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Préparation châssis de la pompe Transfer</t>
+          <t>Serrage des tresse de la pompe IP03A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OR000004240411</t>
+          <t>OR000004208417</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-STFUEL-PPETF1</t>
+          <t>SF01-UT-FDEM-BASSIN-0IP03A</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>POMPE DE TRANSFERT DE FUEL N 01</t>
+          <t>MOTOPOMPE EAU MER VERS PSII IPO3A BASSIN</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>S-PC-PTF1</t>
+          <t>S-PC-P924 IP 03A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7663,7 +7687,7 @@
         <v>46290</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>45728</v>
+        <v>45717</v>
       </c>
       <c r="R82" t="n">
         <v>1</v>
@@ -7687,33 +7711,33 @@
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>4242591</v>
+        <v>4208418</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remise en état caillebotis du CP5</t>
+          <t>Etanchement fuite vapeur au niveau bride</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OR000004242591</t>
+          <t>OR000004208418</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-000CP5</t>
+          <t>SF01-UT-00PC-EAUVAP-20FR04</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CHAINE DE DEMINERALISATION CP5 TED DE MC</t>
+          <t>COLLECTEUR BARILLET VAPEUR MP</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SA-PC-Z12-01</t>
+          <t>S-PC-920FR04</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7750,7 +7774,7 @@
         <v>46290</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>45729</v>
+        <v>45717</v>
       </c>
       <c r="R83" t="n">
         <v>1</v>
@@ -7772,35 +7796,37 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="n">
+        <v>10164242</v>
+      </c>
       <c r="B84" t="n">
-        <v>4292932</v>
+        <v>4210032</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CHANGEMENT LES TRESSES</t>
+          <t>Démontage et remontage deux bruleur</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OR000004292932</t>
+          <t>OR000004210032</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-BAC100</t>
+          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BAC FUEL 100 M3 CHAUDIERE BW MC</t>
+          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>S-PC-BW-CITERNE FUEL</t>
+          <t>S-PC-B2</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7830,14 +7856,14 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>BENMOUSSA1</t>
+          <t>MATAR1</t>
         </is>
       </c>
       <c r="P84" s="2" t="n">
-        <v>45743</v>
+        <v>46290</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>45743</v>
+        <v>45719</v>
       </c>
       <c r="R84" t="n">
         <v>1</v>
@@ -7861,31 +7887,35 @@
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>4434027</v>
+        <v>4210037</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CHANGEMENT D ACCOUPLEMENT</t>
+          <t>Travaux sur diaphragme sortie vapeur BW2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OR000004434027</t>
+          <t>OR000004210037</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SF01-UT-0TED-EAUFLT-PPEF03-TRAN-ACCOUPLE</t>
+          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ACCOUPLEMENT PPE EAU FILTRE CHATEAU N 03</t>
+          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>S-PC-B2</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -7903,7 +7933,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>TCLO CONF IMPR ARCO CCRP ERCT JBFI MMEf*</t>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -7913,14 +7943,14 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>BENMOUSSA1</t>
+          <t>MATAR1</t>
         </is>
       </c>
       <c r="P85" s="2" t="n">
-        <v>45768</v>
+        <v>46290</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>45768</v>
+        <v>45719</v>
       </c>
       <c r="R85" t="n">
         <v>1</v>
@@ -7942,33 +7972,39 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="n">
+        <v>10170802</v>
+      </c>
       <c r="B86" t="n">
-        <v>4434031</v>
+        <v>4210182</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CHANGEMENT LES TRESSES</t>
+          <t>Démontage et remontage pompe Transfer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OR000004434031</t>
+          <t>OR000004210182</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC-000BW2-CHAUDI-CANA</t>
+          <t>SF01-UT-00PC-STFUEL-PPETF1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CANALISATIONS ACCESSOIRES CHAUDIERE BW2</t>
+          <t>POMPE DE TRANSFERT DE FUEL N 01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>S-PC-PTF1</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>SF1-MCU</t>
@@ -7986,7 +8022,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>TCLO CONF ARCO CCRP ERCT JBFI MMEf RIMP</t>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -7996,14 +8032,14 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>BENMOUSSA1</t>
+          <t>MATAR1</t>
         </is>
       </c>
       <c r="P86" s="2" t="n">
-        <v>45768</v>
+        <v>46290</v>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>45768</v>
+        <v>45719</v>
       </c>
       <c r="R86" t="n">
         <v>1</v>
@@ -8025,37 +8061,35 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>13774000</v>
-      </c>
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>4002850160</v>
+        <v>4210188</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>serrage des tresses de la pompe  BP1 ver</t>
+          <t>Démontage et remontage filtre HP au BW</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OR004002850160</t>
+          <t>OR000004210188</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SF01-UT</t>
+          <t>SF01-UT-00PC-EAUVAP-HPVAPE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UTILITE ENERGIE ET FLUIDE MAROC CHIMIE</t>
+          <t>CIRCUIT VAPEUR HP DE LA CENTRALE  PC</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SA-PC-PC</t>
+          <t>S-PC-PC-VAPHP</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8092,7 +8126,7 @@
         <v>46290</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>46290</v>
+        <v>45719</v>
       </c>
       <c r="R87" t="n">
         <v>1</v>
@@ -8116,33 +8150,33 @@
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>4002850230</v>
+        <v>4210191</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Controle des tresses de la pompe BP1 ver</t>
+          <t>Etanchement fuite de vapeur de diaphragm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OR004002850230</t>
+          <t>OR000004210191</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SF01-UT-00PC</t>
+          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CENTRALE THERMIQUE ET ENERGIE DE MC</t>
+          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SA-PC-PC-E</t>
+          <t>S-PC-B2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8179,7 +8213,7 @@
         <v>46290</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>46290</v>
+        <v>45719</v>
       </c>
       <c r="R88" t="n">
         <v>1</v>
@@ -8195,6 +8229,1485 @@
         </is>
       </c>
       <c r="U88" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>10127258</v>
+      </c>
+      <c r="B89" t="n">
+        <v>4210350</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Démontage coude Noria A  pour débouchage</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OR000004210350</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>S-PC-922 IE 01A</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>45719</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>10127275</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4210352</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Démontage coude Noria  B pour débouchage</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OR000004210352</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-0NORIA-0IE01B</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ECHANGEUR NORIA-B CENTRALE MC</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>S-PC-922 IE 01B</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>45719</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>4211596</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Etanchement fuit vapeur sur bruleur BW2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OR000004211596</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>S-PC-B2</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>45720</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>4212499</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Décoincement de la vanne de vapeur BW2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OR000004212499</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>S-PC-B2</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>45720</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>4212565</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Démontage et remontage manchette</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OR000004212565</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>SF01-UT-0TED-000CP5-P1211A</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>MOTOPOMPE DE REPRISE A</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>S-PC-P12-11A</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>45720</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>10127378</v>
+      </c>
+      <c r="B94" t="n">
+        <v>4212573</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Pose chassis de la pompe BP vers PP1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OR000004212573</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>SF01-UT-FDEM-0SEMII-P1303B</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>MOTOPOMPE EAU MER PPI P1303B SEM II MC</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>S-PC-P1303B</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>45720</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>4219072</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Démontage coude Noria A  pour débouchage</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OR000004219072</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-0NORIA-0IE01A</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ECHANGEUR NORIA-A CENTRALE MC</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>S-PC-922 IE 01A</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>45721</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>4219078</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Etanchement deux fuite de vapeur circuit</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OR000004219078</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-000BW2-CHAUDI</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CHAUDIERE AUXLILLAIRE BW2 MC</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>S-PC-B2</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>45721</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>4219849</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>débridage de l'aspiration de la pompe Su</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OR000004219849</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>SF01-UT-FDEM-0SEMII-P1303A</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MOTOPOMPE EAU MER PPI P1303A SEM II MC</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>S-PC-P1303A</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>45721</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>4228040</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Serrage des tresse pompe IP02B</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OR000004228040</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SF01-UT-FDEM-BASSIN-0IP02B</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MOTOPOMPE EAU MER VERS SEM2 IPO2B</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>S-PC-P924 IP 02B</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>45722</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>4240411</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Préparation châssis de la pompe Transfer</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>OR000004240411</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-STFUEL-PPETF1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>POMPE DE TRANSFERT DE FUEL N 01</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>S-PC-PTF1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>45728</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>4242591</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remise en état caillebotis du CP5</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OR000004242591</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>SF01-UT-0TED-000CP5</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>CHAINE DE DEMINERALISATION CP5 TED DE MC</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>SA-PC-Z12-01</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>45729</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>4292932</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CHANGEMENT LES TRESSES</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>OR000004292932</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-000BW2-BAC100</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>BAC FUEL 100 M3 CHAUDIERE BW MC</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>S-PC-BW-CITERNE FUEL</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>BENMOUSSA1</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>45743</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>45743</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>4434027</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CHANGEMENT D ACCOUPLEMENT</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>OR000004434027</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>SF01-UT-0TED-EAUFLT-PPEF03-TRAN-ACCOUPLE</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ACCOUPLEMENT PPE EAU FILTRE CHATEAU N 03</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>TCLO CONF IMPR ARCO CCRP ERCT JBFI MMEf*</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>BENMOUSSA1</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>45768</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>45768</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>4434031</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CHANGEMENT LES TRESSES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>OR000004434031</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC-000BW2-CHAUDI-CANA</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CANALISATIONS ACCESSOIRES CHAUDIERE BW2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>TCLO CONF ARCO CCRP ERCT JBFI MMEf RIMP</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>BENMOUSSA1</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>45768</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>45768</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>13774000</v>
+      </c>
+      <c r="B104" t="n">
+        <v>4002850160</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>serrage des tresses de la pompe  BP1 ver</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OR004002850160</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>SF01-UT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>UTILITE ENERGIE ET FLUIDE MAROC CHIMIE</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>SA-PC-PC</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="R104" t="n">
+        <v>1</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>4002850230</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Controle des tresses de la pompe BP1 ver</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>OR004002850230</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>SF01-UT-00PC</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CENTRALE THERMIQUE ET ENERGIE DE MC</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>SA-PC-PC-E</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>SF1-MCU</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
         <is>
           <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
         </is>
